--- a/Codes_2025/Trial 3/Trial3_LSTM_Followers_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_LSTM_Followers_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,13 +470,13 @@
         <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>5.93</v>
+        <v>37.81</v>
       </c>
       <c r="D2" t="n">
-        <v>6.449515819549561</v>
+        <v>1.207628965377808</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5195158195495608</v>
+        <v>36.60237103462219</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,13 +494,13 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>2.64</v>
+        <v>6.81</v>
       </c>
       <c r="D3" t="n">
-        <v>4.431181907653809</v>
+        <v>1.305057406425476</v>
       </c>
       <c r="E3" t="n">
-        <v>1.791181907653808</v>
+        <v>5.504942593574524</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -518,13 +518,13 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>10.68</v>
+        <v>19.89</v>
       </c>
       <c r="D4" t="n">
-        <v>5.454357147216797</v>
+        <v>1.340225338935852</v>
       </c>
       <c r="E4" t="n">
-        <v>5.225642852783201</v>
+        <v>18.54977466106414</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -542,13 +542,13 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>7.740000000000002</v>
+        <v>8.050000000000002</v>
       </c>
       <c r="D5" t="n">
-        <v>6.212641716003418</v>
+        <v>1.503566741943359</v>
       </c>
       <c r="E5" t="n">
-        <v>1.527358283996584</v>
+        <v>6.546433258056643</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -566,13 +566,13 @@
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>37.81</v>
+        <v>7.989999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>7.479279518127441</v>
+        <v>1.423897981643677</v>
       </c>
       <c r="E6" t="n">
-        <v>30.33072048187256</v>
+        <v>6.566102018356323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -590,13 +590,13 @@
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>6.81</v>
+        <v>28.09</v>
       </c>
       <c r="D7" t="n">
-        <v>7.500354290008545</v>
+        <v>1.528224945068359</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6903542900085453</v>
+        <v>26.56177505493164</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>19.89</v>
+        <v>33.88</v>
       </c>
       <c r="D8" t="n">
-        <v>6.561531066894531</v>
+        <v>1.280932664871216</v>
       </c>
       <c r="E8" t="n">
-        <v>13.32846893310547</v>
+        <v>32.59906733512879</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -638,13 +638,13 @@
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>8.050000000000002</v>
+        <v>24.26000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>5.526406288146973</v>
+        <v>1.175751090049744</v>
       </c>
       <c r="E9" t="n">
-        <v>2.52359371185303</v>
+        <v>23.08424890995026</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -662,13 +662,13 @@
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>7.989999999999999</v>
+        <v>5.56</v>
       </c>
       <c r="D10" t="n">
-        <v>6.056863307952881</v>
+        <v>1.504428267478943</v>
       </c>
       <c r="E10" t="n">
-        <v>1.933136692047118</v>
+        <v>4.055571732521057</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -686,111 +686,15 @@
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>28.09</v>
+        <v>11.6</v>
       </c>
       <c r="D11" t="n">
-        <v>6.403787136077881</v>
+        <v>1.21905791759491</v>
       </c>
       <c r="E11" t="n">
-        <v>21.68621286392212</v>
+        <v>10.38094208240509</v>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C12" t="n">
-        <v>33.88</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4.493781089782715</v>
-      </c>
-      <c r="E12" t="n">
-        <v>29.38621891021729</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C13" t="n">
-        <v>24.26000000000001</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7.678126811981201</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.5818731880188</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="D14" t="n">
-        <v>6.729555606842041</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.169555606842041</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C15" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6.411301612854004</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5.188698387145998</v>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>Followers</t>
         </is>

--- a/Codes_2025/Trial 3/Trial3_LSTM_Followers_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_LSTM_Followers_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,10 +473,10 @@
         <v>37.81</v>
       </c>
       <c r="D2" t="n">
-        <v>1.207628965377808</v>
+        <v>1.488888263702393</v>
       </c>
       <c r="E2" t="n">
-        <v>36.60237103462219</v>
+        <v>36.32111173629761</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,13 +494,13 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>6.81</v>
+        <v>19.89</v>
       </c>
       <c r="D3" t="n">
-        <v>1.305057406425476</v>
+        <v>1.80122697353363</v>
       </c>
       <c r="E3" t="n">
-        <v>5.504942593574524</v>
+        <v>18.08877302646637</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -518,13 +518,13 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>19.89</v>
+        <v>8.050000000000002</v>
       </c>
       <c r="D4" t="n">
-        <v>1.340225338935852</v>
+        <v>2.239750146865845</v>
       </c>
       <c r="E4" t="n">
-        <v>18.54977466106414</v>
+        <v>5.810249853134158</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -542,13 +542,13 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>8.050000000000002</v>
+        <v>7.989999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.503566741943359</v>
+        <v>1.837335348129272</v>
       </c>
       <c r="E5" t="n">
-        <v>6.546433258056643</v>
+        <v>6.152664651870727</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +559,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>7.989999999999999</v>
+        <v>33.88</v>
       </c>
       <c r="D6" t="n">
-        <v>1.423897981643677</v>
+        <v>1.678048729896545</v>
       </c>
       <c r="E6" t="n">
-        <v>6.566102018356323</v>
+        <v>32.20195127010346</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>28.09</v>
+        <v>5.56</v>
       </c>
       <c r="D7" t="n">
-        <v>1.528224945068359</v>
+        <v>1.365822553634644</v>
       </c>
       <c r="E7" t="n">
-        <v>26.56177505493164</v>
+        <v>4.194177446365356</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,94 +607,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>33.88</v>
+        <v>11.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.280932664871216</v>
+        <v>1.573182106018066</v>
       </c>
       <c r="E8" t="n">
-        <v>32.59906733512879</v>
+        <v>10.02681789398194</v>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Latvia</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C9" t="n">
-        <v>24.26000000000001</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.175751090049744</v>
-      </c>
-      <c r="E9" t="n">
-        <v>23.08424890995026</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.504428267478943</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4.055571732521057</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C11" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.21905791759491</v>
-      </c>
-      <c r="E11" t="n">
-        <v>10.38094208240509</v>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>Followers</t>
         </is>
